--- a/shucle_report/백운면/20260101_20260325/report_백운면_20260101_20260325.xlsx
+++ b/shucle_report/백운면/20260101_20260325/report_백운면_20260101_20260325.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.01.01 ~ 03.25 | 비교기간: 2025.10.01 ~ 12.30 | 생성: 2026-03-26 13:09 | 차트: 118개</t>
+          <t>분석기간: 2026.01.01 ~ 03.25 | 비교기간: 2025.10.01 ~ 12.30 | 생성: 2026-03-26 14:48 | 차트: 118개</t>
         </is>
       </c>
     </row>
@@ -952,22 +952,22 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>234km</t>
+          <t>229km</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>229km</t>
+          <t>224km</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>-5.1km</t>
+          <t>-5.4km</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1063,22 +1063,22 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>2.5명</t>
+          <t>2.2명</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>1.8명</t>
+          <t>1.1명</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>-0.6명</t>
+          <t>-1.1명</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-48.0%</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -1527,17 +1527,17 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>+4.5</t>
+          <t>+3.2</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>평일 26.5분 (20% 증가)</t>
+          <t>평일 18.9분 (20% 증가)</t>
         </is>
       </c>
     </row>
@@ -1564,17 +1564,17 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>주말 19.1분 (13% 감소)</t>
+          <t>주말 5.5분 (13% 감소)</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>▼ 신규 지역 회원(일평균) (-25.2%)</t>
+          <t>▼ 신규 지역 회원(일평균) (-48.0%)</t>
         </is>
       </c>
     </row>
@@ -1911,27 +1911,27 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>547</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>464</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>+136.0</t>
+          <t>-82.3</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>+22.1%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>누적 750명 (22% 증가)</t>
+          <t>누적 464명 (15% 감소)</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>• 성장 지표 긍정적: 신규회원 2→2명(-25%), 누적 797명</t>
+          <t>• 성장 지표 긍정적: 신규회원 2→1명(-48%), 누적 797명</t>
         </is>
       </c>
     </row>
@@ -2499,17 +2499,17 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>+5.2</t>
+          <t>+3.7</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>평일 30.1명 (21% 증가)</t>
+          <t>평일 21.5명 (21% 증가)</t>
         </is>
       </c>
     </row>
@@ -2536,17 +2536,17 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>주말 20.9명 (18% 감소)</t>
+          <t>주말 6.0명 (18% 감소)</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>▼ 대당 운행거리(일평균) (-2.2%)</t>
+          <t>▼ 대당 운행거리(일평균) (-2.4%)</t>
         </is>
       </c>
     </row>
@@ -3348,22 +3348,22 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>229</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
